--- a/APP_(Izmantojot_27.10.2025_lekcijas_kodu_as_template)/app/models/recipe.xlsx
+++ b/APP_(Izmantojot_27.10.2025_lekcijas_kodu_as_template)/app/models/recipe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P35E\Downloads\8.01.2026\jaunie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910C5618-A468-41D8-B89A-00C707D7A605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF33F499-EED4-49BD-88C4-0D79126C191F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="4785" windowWidth="22395" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -680,7 +680,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Parasts" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -897,23 +897,23 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" customWidth="1"/>
-    <col min="8" max="8" width="4.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" customWidth="1"/>
-    <col min="14" max="14" width="52.85546875" customWidth="1"/>
-    <col min="15" max="15" width="26.28515625" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="8" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="46.28515625" customWidth="1"/>
+    <col min="15" max="15" width="63.85546875" customWidth="1"/>
+    <col min="16" max="16" width="22.28515625" customWidth="1"/>
+    <col min="17" max="17" width="34.5703125" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
     <col min="19" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
